--- a/小野町_引継ぎ_整理済/11_見える化出力依頼/小野町_見える化システム入力値一覧_20260924.xlsx
+++ b/小野町_引継ぎ_整理済/11_見える化出力依頼/小野町_見える化システム入力値一覧_20260924.xlsx
@@ -557,7 +557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -636,7 +636,7 @@
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>**令和8年度の列は1か月分である。**2_サービス別給付費 の人数・回数・日数を数えると、令和8年度は非ゼロ36件のうち31件（86.1％）が整数であるのに対し、令和6年度は46件中5件（10.9％）、令和7年度は40件中8件（20.0％）にとどまる。令和6・7年度は12分の1単位の小数（年間延べ÷12）である</t>
+          <t>**令和8年度の列は1か月分である。**2_サービス別給付費 の人数・回数・日数を数えると、令和8年度は非ゼロ36件のうち31件（86.1％）が整数であるのに対し、令和6年度は46件中5件（10.9％）、令和7年度は40件中8件（20.0％）にとどまる。令和6・7年度は12分の1単位の小数（年間延べ÷12）である。**国保連月報でみると、令和8年度4〜6月提供分の給付額は前年の同じ月の96.0％である。**令和8年度を自然体推計に置き換えるときは、この水準が目安になる</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,14 @@
     <row r="19">
       <c r="A19" s="14" t="inlineStr">
         <is>
-          <t>**※ 入力しても当方の算定と同じ数字にはならない。**見える化の認定者数は各年9月末、当方は年度末で、基準日が違うためである。差は05_出力後に突き合わせる に整理した。</t>
+          <t>**※ 入力しても当方の算定と同じ数字にはならない。**見える化の認定者数は各年9月末、当方は年度末で、基準日が違うためである。差は04_出力後に突き合わせる に整理した。</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="14" t="inlineStr">
+        <is>
+          <t>**※ ワークシートの給付費の列は、年度のラベルと中身が合っていない。**「令和6年度」の列はサービス別に突き合わせると21件中20件で年報の令和5年度と比が1.000になる（1年ずれている）。「令和7年度」は年報のどの年度とも完全には一致せず、令和7年度と中央値0.9959で近い。**実績として読むときは指標ごと・列ごとに年度を確かめる必要がある。**</t>
         </is>
       </c>
     </row>
@@ -3025,10 +3032,10 @@
         <v>841</v>
       </c>
       <c r="C4" s="19" t="n">
-        <v>780</v>
+        <v>772</v>
       </c>
       <c r="D4" s="25" t="n">
-        <v>-61</v>
+        <v>-69</v>
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
